--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -981,7 +981,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1007,6 +1007,11 @@
       <c r="I14" t="n">
         <v>2302171</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>manual-dh-mcea-电缸操作手册</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1066,7 +1071,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1092,6 +1097,11 @@
       <c r="I16" t="n">
         <v>672972</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>manual-sac-np2-param-import-export</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1281,7 +1291,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1307,6 +1317,11 @@
       <c r="I21" t="n">
         <v>2290643</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>manual-dh-pgia-pgea-电爪操作手册</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1404,7 +1419,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1430,6 +1445,11 @@
       <c r="I24" t="n">
         <v>1560</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>manual-sac-usb-upgrade</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1484,7 +1504,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1510,6 +1530,11 @@
       <c r="I26" t="n">
         <v>2472</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>manual-sac-n2-xml-update</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1524,7 +1549,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1549,6 +1574,11 @@
       </c>
       <c r="I27" t="n">
         <v>3487</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>manual-sac-xml-modify</t>
+        </is>
       </c>
     </row>
     <row r="28">

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>编译页</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mtime</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>size</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>编译页</t>
         </is>
       </c>
     </row>
@@ -494,17 +494,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>778ed9df34436a46aa313992d70d2207e6177f12a21ff2f6b38de8021e581f8c</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2023-09-15T09:54:12</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>66634</v>
       </c>
     </row>
@@ -534,17 +534,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>b95d4c5f9a7bf608bebbf9165ed2c4487a0ff8b9554d93fc53c2df4b97a0e825</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2023-12-05T19:40:27</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>36645088</v>
       </c>
     </row>
@@ -574,17 +574,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>44411402c048885480bd651a0794c609934caa7e9804682317f1183c1576ae6f</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2023-12-19T15:16:36</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2671999</v>
       </c>
     </row>
@@ -614,17 +614,17 @@
           <t>电爪</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>144535e9bd3db9215c0eb09ef05f2c9e372af4f0a5d0469b410573402cc1f00f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2024-02-01T19:10:53</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2123207</v>
       </c>
     </row>
@@ -654,17 +654,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>7f8c17af54f1fc5d1d1d9c33396369190160739e05399b865a2ee6ea3200b953</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2024-02-20T15:30:20</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>2885231</v>
       </c>
     </row>
@@ -699,17 +699,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1fd051673fbaff0aac031b2950ddff12327d2db454bb21eec0f04cfb92621730</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2024-04-13T16:00:38</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>7879765</v>
       </c>
     </row>
@@ -739,17 +739,17 @@
           <t>电缸;电爪</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>be8d59014a3825daa02c53e12eed2fe775240a42caa79472d45cfbe3582f6cd4</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2024-05-18T14:50:16</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1214170</v>
       </c>
     </row>
@@ -779,17 +779,17 @@
           <t>电缸;电爪</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>b3e0c5a4820fd17e23908c02df96aabd1d88d4231be79ef0698bcf9f812cbea6</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2025-02-22T13:09:48</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1309131</v>
       </c>
     </row>
@@ -819,17 +819,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>07a5287d16f431d27fe5027901ce452d64a96d15e7c0b2af423f1c89ee178bb4</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2024-05-24T20:29:52</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1608601</v>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -866,15 +866,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>manual-dh-电缸软重启</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>d0c534458402d38f55a5a8d07e43adc636f09f4b5a4f3c1b719abf234365ebe8</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2024-08-19T14:39:52</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1187994</v>
       </c>
     </row>
@@ -909,17 +914,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1ec4b0315b7949dbc504d51184c69a91f695aa14f593bcd081b6dc00299d8b21</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2024-10-29T19:47:55</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>774862</v>
       </c>
     </row>
@@ -949,17 +954,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>ce39b1dc94cdbc266b0d29ae2d067c64086e7e15ac7549e9b72f7dd9c7988018</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-01-22T10:32:33</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>63902599</v>
       </c>
     </row>
@@ -996,21 +1001,21 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>manual-dh-mcea-电缸操作手册</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0e4ec41a7834d47d7bbed14b5bd6eed249c99eedfda40e91bba9926af3a4c3a5</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-02-06T11:19:30</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2302171</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>manual-dh-mcea-电缸操作手册</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1031,7 +1036,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1041,20 +1046,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>驱动器</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>manual-sac-nf2-force-control</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>bc52d1ee1daa6c6351276464c68e28100e4b7e7a46e6043f0d5c94cd1fb828ec</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2026-03-05T10:36:44</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>2047685</v>
       </c>
     </row>
@@ -1086,21 +1096,21 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>manual-sac-np2-param-import-export</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>b95d526eddb8e60a3b6a06990464cacb40a20ae8b1fbcaabeb75a5d691c70633</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2026-04-08T09:44:46</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>672972</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>manual-sac-np2-param-import-export</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1121,7 +1131,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1136,15 +1146,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>manual-sac-np2-product</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>12e646b5f2c9546b77dfb4b76d3e37dc7f6c691f831ed4794086c21570163546</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2026-04-13T13:53:38</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2337391</v>
       </c>
     </row>
@@ -1161,7 +1176,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1176,15 +1191,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>manual-sac-n2-first-power-on-sop</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>f14ae224121785fe6d1f87e59e397ceb9a5803d76bd97376c6b20086955be525</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2026-04-15T18:58:22</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>2471087</v>
       </c>
     </row>
@@ -1214,17 +1234,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>eda3619ac088900d78c342a0bed1a7925b1e44796596f871abaf5995d1d433b7</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>2026-04-16T14:57:38</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2355994</v>
       </c>
     </row>
@@ -1246,7 +1266,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1261,15 +1281,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>manual-sac-n2-driver-debug-sop</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>aec7b8dad66ce13080f4f9a8e365055c067159bb1df0d8ac753d8350ff7c4342</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2026-05-08T21:47:04</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>4728798</v>
       </c>
     </row>
@@ -1306,21 +1331,21 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>manual-dh-pgia-pgea-电爪操作手册</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>c60d6224660fda89a384532dc84b51bfb062eb5cc90cacbb91680a6aabf37c00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>2026-05-27T17:57:02</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>2290643</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>manual-dh-pgia-pgea-电爪操作手册</t>
-        </is>
       </c>
     </row>
     <row r="22">
@@ -1339,7 +1364,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1354,15 +1379,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>manual-dh-电爪抱闸时间修改</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>09273fd4ef3995f21a4ebf43ef352e91721c8e9b1e273feeef2262998685bc0f</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>2026-08-18T16:14:39</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1239650</v>
       </c>
     </row>
@@ -1379,7 +1409,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1394,15 +1424,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>manual-sac-n2-motor-tuning</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>6461ce8a8c317fe1f73006047844306cff9b16900f2746972f658ccea4a02105</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>2026-08-18T16:29:29</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>8480</v>
       </c>
     </row>
@@ -1434,21 +1469,21 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>manual-sac-usb-upgrade</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>e98b999e26a328f0b6e09bf2b4a7253ef694ef2c45dbfd81d36d2e61ccfc3df5</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2026-08-18T16:29:51</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1560</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>manual-sac-usb-upgrade</t>
-        </is>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1499,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1479,15 +1514,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>manual-sac-n2-ethercat-application</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>04a2b0c588387106e97db914fe432dcbb145fc4ab036eeb9160dfa176ed4e5f2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>2026-08-18T16:30:39</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>51410</v>
       </c>
     </row>
@@ -1519,21 +1559,21 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>manual-sac-n2-xml-update</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>6919c960afa484293ca200ef5485feccb98a72eab8bff3b4ec51ac13f1cf3eb0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>2026-08-18T16:31:29</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>2472</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>manual-sac-n2-xml-update</t>
-        </is>
       </c>
     </row>
     <row r="27">
@@ -1564,21 +1604,21 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>manual-sac-xml-modify</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>6083ed9a39f938f22baba813c5cfc80054ab93aeb8274f2a334e33b9983978a4</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2026-08-18T16:31:41</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>3487</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>manual-sac-xml-modify</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -1607,17 +1647,17 @@
           <t>电缸;电爪</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>50993694c90f3263afbc1fc4f29bf0af7fb66b7f142da3cd6ed1be739daf2086</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2023-10-07T09:59:42</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>974341</v>
       </c>
     </row>
@@ -1652,17 +1692,17 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>47159ff136cf0866686ebdb0fd63f215db09f3350be24e7410e3f46cbc440d40</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2024-11-19T14:47:28</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>7390077</v>
       </c>
     </row>
@@ -1697,17 +1737,17 @@
           <t>驱动器</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2c385359f9b72a3fc4935c63d7c3a6e7817f7dba6bb46a93f9a2e0b73aac02c0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>2024-12-16T19:37:34</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>85383</v>
       </c>
     </row>
@@ -1742,17 +1782,17 @@
           <t>电缸</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>e2a087fbea74a03c9f0572398ebb0957b414626974765ec28dd26dc264b50e53</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2025-03-16T21:45:00</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>8903176</v>
       </c>
     </row>
@@ -1787,17 +1827,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>f358597b7dbfbce41545175ca395aed9bc14da4185cb2f3d4c56d94f5e907c39</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>2025-03-16T21:45:02</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>8104651</v>
       </c>
     </row>
@@ -1832,17 +1872,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>c64d5265cdd016b3afe90869792673b9e640c4331fdf062cdbb357f65dca9ec4</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>2025-06-03T16:07:01</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>13143563</v>
       </c>
     </row>
@@ -1877,17 +1917,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>5e13cb2ff9aac044ee3a74d184e69fbc683315628e860637a23a7100076d6463</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2025-06-07T12:21:06</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>13126647</v>
       </c>
     </row>
@@ -1922,17 +1962,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>d3674a0e36c51a60514cfc0f8c8d3265c0a0e305fde9410ef66ae91033605496</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>2025-08-13T17:26:12</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>7839955</v>
       </c>
     </row>
@@ -1967,17 +2007,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>1261dad1b34d1d6fd2ae099c7c90800407664a0d4cee8afb1b54c8bfedd6c304</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>2025-08-13T17:30:33</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8036364</v>
       </c>
     </row>
@@ -2012,17 +2052,17 @@
           <t>音圈电机</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>a465cc4a301afa3d2536b075442db611f21ee147518c103a523c8d5b4aed1803</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>2025-09-01T16:20:24</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>7911751</v>
       </c>
     </row>
@@ -2057,17 +2097,17 @@
           <t>电爪;音圈电机</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>48043027812023438d35ecce8dd7fc4549d14ac6c22e18181e505e5e0fcbee64</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>2026-08-18T15:58:10</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>92825447</v>
       </c>
     </row>
@@ -2087,7 +2127,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2102,15 +2142,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>manual-dh-电缸报警代码解析</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>34c0f523c106c80526171d4010b0cf7b0297249776066a669329410528ab894e</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2024-11-11T14:11:39</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>18015</v>
       </c>
     </row>
@@ -2127,7 +2172,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2142,15 +2187,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>manual-sac-n2-faq</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>f0b284d3f0de8c09e18d1e28423c370e37814e85519c8dc572544cf70fa6c6d9</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>2026-08-18T16:31:02</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>4894</v>
       </c>
     </row>
@@ -2170,7 +2220,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2185,15 +2235,20 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>manual-dh-电缸选型手册</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>de35032c834b8dff40dbaee84e848811ce46382fe232755af9fef903a15925df</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>2026-08-04T06:48:20</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>44597335</v>
       </c>
     </row>
@@ -2210,20 +2265,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>新增待归类</t>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>电爪</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>manual-dh-pgls-电爪校准偏置值</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>8137613e90dac3d639e4a3cd0292499a67caa78c63fc001a8eed1002c22e867f</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>2026-06-02T23:44:32</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>2234060</v>
       </c>
     </row>
@@ -2260,21 +2325,21 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>manual-dh-电爪选型手册</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>884d95959b0232df534f6b38f40c9966494a972073a7d0b17b415a63b8f31dab</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>2026-08-18T22:04:19</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>52855715</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>manual-dh-电爪选型手册</t>
-        </is>
       </c>
     </row>
     <row r="44">
@@ -2310,21 +2375,21 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>manual-dh-音圈选型手册</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>253e3398fab59cf0667ce8b5cddbacedf2499c204807ad6ec6059eeb555aa454</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>2026-08-18T22:06:39</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>7095953</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>manual-dh-音圈选型手册</t>
-        </is>
       </c>
     </row>
     <row r="45">
@@ -2353,18 +2418,198 @@
           <t>电爪;电缸</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>41cf18afa563cd7a5f5e2acb44f73dfd3e28b6035f29dcaba8e914ab49d27f3b</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>2026-08-18T22:07:28</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>22977281</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PGLS寄存器_20260818.xlsx</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>电爪</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>manual-dh-485寄存器表总览</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8e236150974420fbed2fe219e454fbcdbfda817ab96637eb9c2bea28c60e7790</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-18T23:54:20</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>22887</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>一体式电缸寄存器表_20260818.xlsx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>电缸</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>manual-dh-485寄存器表总览</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>979fcaa89f99f6a1705a1712e549a9dc64f936d0ea06e4a80048c7bcaa23d341</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:01:53</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>24635</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>分体式电缸寄存器表_20260818.xlsx</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>电缸</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>manual-dh-485寄存器表总览</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>23a3e69a01d96c2de017c4d41cdda1e3cd9ce0b901142ad9e68c6243f31fb0b7</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:01:26</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>38778</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>电爪寄存器_20260818.xlsx</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>电爪</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>manual-dh-485寄存器表总览</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3561e0ac088d40334255fd9ac43f9e779957a6dc1e1e5d251088dff986a8b088</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:01:01</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>83168</v>
       </c>
     </row>
   </sheetData>

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -492,6 +492,11 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>通用</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>concept-开环力控</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,7 +606,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -612,6 +617,11 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>电爪</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>manual-dh-夹爪固件升级</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -641,7 +651,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -652,6 +662,11 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>通用</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>manual-xjc-608t-操作说明SOP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -726,7 +741,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -737,6 +752,11 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>manual-dh-ecat盒子固件升级</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -766,7 +786,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -777,6 +797,11 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>manual-dh-ecat盒子固件升级</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -806,7 +831,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -816,7 +841,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>电爪</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>manual-dh-旋转零点校准</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -901,7 +931,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -912,6 +942,11 @@
       <c r="F12" t="inlineStr">
         <is>
           <t>通用</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>manual-dh-电气篇应用指导</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1221,7 +1256,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1232,6 +1267,11 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>通用</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>manual-鑫精诚力显示器参数修改说明</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1634,7 +1674,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1645,6 +1685,11 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>manual-dh-基恩士适配ecat盒子</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1679,7 +1724,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1689,7 +1734,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>通用</t>
+          <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>manual-dh-三菱卓岚通讯配置</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1724,7 +1774,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1735,6 +1785,11 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>驱动器</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>manual-sac-对象字典</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1769,7 +1824,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1780,6 +1835,11 @@
       <c r="F31" t="inlineStr">
         <is>
           <t>电缸</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1814,7 +1874,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1825,6 +1885,11 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1859,7 +1924,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1870,6 +1935,11 @@
       <c r="F33" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1904,7 +1974,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1915,6 +1985,11 @@
       <c r="F34" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1949,7 +2024,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1960,6 +2035,11 @@
       <c r="F35" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1994,7 +2074,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2005,6 +2085,11 @@
       <c r="F36" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2039,7 +2124,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>在库</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2050,6 +2135,11 @@
       <c r="F37" t="inlineStr">
         <is>
           <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>manual-dh-控制卡适配技术样本</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2405,7 +2495,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>在库待编译</t>
+          <t>已编译</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2415,7 +2505,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>电爪;电缸</t>
+          <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>manual-dh-m2e-b1-4通讯盒使用说明</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2610,6 +2705,51 @@
       </c>
       <c r="J49" t="n">
         <v>83168</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SAC伺服驱动器报警代码表_20260819.xlsx</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>驱动器</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>manual-sac-伺服驱动器报警代码表</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>54b72c744eaac3637248fbc1660db5be974b1ce1a00d9565e671767fc27c92f3</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:59:15</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>17154</v>
       </c>
     </row>
   </sheetData>

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2752,6 +2752,214 @@
         <v>17154</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>噗元FAQ_20250424.xlsx</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>20250424</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>电爪;电缸;音圈电机;驱动器</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>faq-电爪;faq-电缸;faq-直驱;faq-驱动器;faq-通讯盒</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>9bf2701755490c4dc5f213da714bdf1823c9cf32a10bb8c936ffd354d6892616</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:13:26</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>55857</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DLAR-20-40-H1节拍测试-SAC-N2_20260819.xlsx</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>音圈电机</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>topic-性能测试-直驱</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>c4f1e54edd2810db7d09660e0de1c386c3f92cde3f63239d041aa5ec202fed62</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:16:28</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>3987821</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MCE-3G&amp;3WG-02-50测试数据与结论_20260819.xlsx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>电缸</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>topic-性能测试-电缸</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>9639a4ebcecb4bffec2389381dc83c673f2491eeb4acd408624001c607b08cad</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-08-19T11:16:29</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>610956</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RGI-100-14旋转力测试_20260819.xlsx</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>性能测试</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>电爪</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>topic-性能测试-电爪</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>87ac8b4d8e64b962cea75e5552d4e9eefd17e19c8754accc2c6a48fb473149dc</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-02-06T11:34:48</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>597549</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2960,6 +2960,110 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>电缸电爪基础考试_20260819.docx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>考试</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>topic-电缸电爪基础考试题库</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>04e129e2841d16e7fcc0d1d6dfb866d0b451d2178c3bdcbe6d87714394201637</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-07-31T09:28:53</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>19292</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>电缸电爪基础考试_20260819_答案.docx</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>考试答案</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>20260819</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>电缸;电爪</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>topic-电缸电爪基础考试题库</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>d99af121c5eeb9362783b25edd6190d06e113bba78800e645cae2f136b1a84a1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-08-19T15:40:27</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>21948</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3064,6 +3064,58 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>华东工单提取仅技术服务&amp;高价值FAQ_20260820.xlsx</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>工单FAQ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>电爪;电缸;音圈/直驱;驱动</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>topic-华东工单案例库</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>ba4241af55d67696d13cd2b9a0099093ddc21f62cfdde3fcf051638b83717d8f</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-08-20T16:17:42</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>950839</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/raw/MANIFEST.xlsx
+++ b/raw/MANIFEST.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>已编译</t>
+          <t>已归档（被 V3.4 取代）</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>manual-dh-pgia-pgea-电爪操作手册</t>
+          <t>manual-dh-pgia-pgea-电爪操作手册（历史版本 V3.3）</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2798,10 +2798,8 @@
           <t>2026-08-19T11:13:26</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>55857</t>
-        </is>
+      <c r="J51" t="n">
+        <v>55857</v>
       </c>
     </row>
     <row r="52">
@@ -2850,10 +2848,8 @@
           <t>2026-08-19T11:16:28</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>3987821</t>
-        </is>
+      <c r="J52" t="n">
+        <v>3987821</v>
       </c>
     </row>
     <row r="53">
@@ -2902,10 +2898,8 @@
           <t>2026-08-19T11:16:29</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>610956</t>
-        </is>
+      <c r="J53" t="n">
+        <v>610956</v>
       </c>
     </row>
     <row r="54">
@@ -2954,10 +2948,8 @@
           <t>2026-02-06T11:34:48</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>597549</t>
-        </is>
+      <c r="J54" t="n">
+        <v>597549</v>
       </c>
     </row>
     <row r="55">
@@ -3006,10 +2998,8 @@
           <t>2026-07-31T09:28:53</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>19292</t>
-        </is>
+      <c r="J55" t="n">
+        <v>19292</v>
       </c>
     </row>
     <row r="56">
@@ -3058,10 +3048,8 @@
           <t>2026-08-19T15:40:27</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>21948</t>
-        </is>
+      <c r="J56" t="n">
+        <v>21948</v>
       </c>
     </row>
     <row r="57">
@@ -3110,10 +3098,58 @@
           <t>2026-08-20T16:17:42</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>950839</t>
-        </is>
+      <c r="J57" t="n">
+        <v>950839</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PGIA.PGEA系列操作手册V3.4.pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>手册</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>V3.4</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>已编译</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>电爪</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>manual-dh-pgia-pgea-电爪操作手册</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>e04ae16f6388ff9989778e50b2d0a1c85490c41b68d5a30d219e4fbbfdea9d1c</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:40:39</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>849674</v>
       </c>
     </row>
   </sheetData>
